--- a/data_sources/Diagnosticos.xlsx
+++ b/data_sources/Diagnosticos.xlsx
@@ -455,11 +455,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cardiovascular</t>
+          <t>Neurológico</t>
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45958.16805555556</v>
+        <v>45911.5803125</v>
       </c>
     </row>
     <row r="3">
@@ -475,11 +475,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Respiratorio</t>
+          <t>Digestivo</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46091.05148148148</v>
+        <v>46163.48138888889</v>
       </c>
     </row>
     <row r="4">
@@ -495,11 +495,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Neurológico</t>
+          <t>Traumatológico</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45999.63193287037</v>
+        <v>45752.21601851852</v>
       </c>
     </row>
     <row r="5">
@@ -515,11 +515,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Respiratorio</t>
+          <t>Neurológico</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46131.35435185185</v>
+        <v>46116.92168981482</v>
       </c>
     </row>
     <row r="6">
@@ -535,11 +535,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Respiratorio</t>
+          <t>Traumatológico</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46116.48998842593</v>
+        <v>46059.99722222222</v>
       </c>
     </row>
     <row r="7">
@@ -555,11 +555,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Traumatológico</t>
+          <t>Respiratorio</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46176.05008101852</v>
+        <v>45961.75207175926</v>
       </c>
     </row>
     <row r="8">
@@ -575,11 +575,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Respiratorio</t>
+          <t>Digestivo</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46109.35163194445</v>
+        <v>45701.84972222222</v>
       </c>
     </row>
     <row r="9">
@@ -595,11 +595,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Digestivo</t>
+          <t>Traumatológico</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45719.58564814815</v>
+        <v>45889.7094212963</v>
       </c>
     </row>
     <row r="10">
@@ -615,11 +615,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Respiratorio</t>
+          <t>Digestivo</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45926.45439814815</v>
+        <v>46070.39630787037</v>
       </c>
     </row>
     <row r="11">
@@ -635,11 +635,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Respiratorio</t>
+          <t>Ginecológico</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45745.3675</v>
+        <v>45995.35012731481</v>
       </c>
     </row>
     <row r="12">
@@ -655,11 +655,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Neurológico</t>
+          <t>Digestivo</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45844.53689814815</v>
+        <v>46172.29709490741</v>
       </c>
     </row>
     <row r="13">
@@ -675,11 +675,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Traumatológico</t>
+          <t>Respiratorio</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45914.06744212963</v>
+        <v>46189.8490625</v>
       </c>
     </row>
     <row r="14">
@@ -695,11 +695,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Respiratorio</t>
+          <t>Ginecológico</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45803.01626157408</v>
+        <v>46133.58475694444</v>
       </c>
     </row>
     <row r="15">
@@ -715,11 +715,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Neurológico</t>
+          <t>Digestivo</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45854.98662037037</v>
+        <v>46109.93413194444</v>
       </c>
     </row>
     <row r="16">
@@ -735,11 +735,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Neurológico</t>
+          <t>Ginecológico</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45793.57064814815</v>
+        <v>45685.10681712963</v>
       </c>
     </row>
     <row r="17">
@@ -755,11 +755,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Respiratorio</t>
+          <t>Ginecológico</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45888.12335648148</v>
+        <v>45865.45395833333</v>
       </c>
     </row>
     <row r="18">
@@ -775,11 +775,11 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Neurológico</t>
+          <t>Traumatológico</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45962.08653935185</v>
+        <v>45775.0896875</v>
       </c>
     </row>
     <row r="19">
@@ -795,11 +795,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Traumatológico</t>
+          <t>Cardiovascular</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45725.33954861111</v>
+        <v>46104.43833333333</v>
       </c>
     </row>
     <row r="20">
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46043.77606481482</v>
+        <v>45828.53706018518</v>
       </c>
     </row>
     <row r="21">
@@ -835,11 +835,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Digestivo</t>
+          <t>Cardiovascular</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45880.97949074074</v>
+        <v>45972.49037037037</v>
       </c>
     </row>
     <row r="22">
@@ -855,11 +855,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Respiratorio</t>
+          <t>Neurológico</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45663.71641203704</v>
+        <v>45792.11509259259</v>
       </c>
     </row>
     <row r="23">
@@ -875,11 +875,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Digestivo</t>
+          <t>Respiratorio</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46195.97341435185</v>
+        <v>46068.28796296296</v>
       </c>
     </row>
     <row r="24">
@@ -895,11 +895,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Digestivo</t>
+          <t>Neurológico</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45910.86804398148</v>
+        <v>45821.94634259259</v>
       </c>
     </row>
     <row r="25">
@@ -915,11 +915,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Digestivo</t>
+          <t>Respiratorio</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45987.4549537037</v>
+        <v>45955.22861111111</v>
       </c>
     </row>
     <row r="26">
@@ -935,11 +935,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Respiratorio</t>
+          <t>Neurológico</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45971.06787037037</v>
+        <v>45853.35856481481</v>
       </c>
     </row>
     <row r="27">
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46108.63101851852</v>
+        <v>45940.80789351852</v>
       </c>
     </row>
     <row r="28">
@@ -975,11 +975,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Neurológico</t>
+          <t>Ginecológico</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45926.86856481482</v>
+        <v>45998.00883101852</v>
       </c>
     </row>
     <row r="29">
@@ -995,11 +995,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cardiovascular</t>
+          <t>Ginecológico</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45865.65881944444</v>
+        <v>45872.95412037037</v>
       </c>
     </row>
     <row r="30">
@@ -1015,11 +1015,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Digestivo</t>
+          <t>Traumatológico</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46123.02778935185</v>
+        <v>46056.98650462963</v>
       </c>
     </row>
     <row r="31">
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45755.91489583333</v>
+        <v>45789.76864583333</v>
       </c>
     </row>
     <row r="32">
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45944.84248842593</v>
+        <v>45679.86902777778</v>
       </c>
     </row>
     <row r="33">
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45839.01392361111</v>
+        <v>45699.53835648148</v>
       </c>
     </row>
     <row r="34">
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46115.53135416667</v>
+        <v>45915.54344907407</v>
       </c>
     </row>
     <row r="35">
@@ -1115,11 +1115,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Digestivo</t>
+          <t>Cardiovascular</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45663.60672453704</v>
+        <v>45841.44516203704</v>
       </c>
     </row>
     <row r="36">
@@ -1135,11 +1135,11 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Digestivo</t>
+          <t>Neurológico</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45789.14174768519</v>
+        <v>46043.67459490741</v>
       </c>
     </row>
     <row r="37">
@@ -1155,11 +1155,11 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cardiovascular</t>
+          <t>Respiratorio</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46088.08724537037</v>
+        <v>45842.22280092593</v>
       </c>
     </row>
     <row r="38">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45689.33074074074</v>
+        <v>45987.77672453703</v>
       </c>
     </row>
     <row r="39">
@@ -1195,11 +1195,11 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cardiovascular</t>
+          <t>Traumatológico</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46151.95863425926</v>
+        <v>45754.20666666667</v>
       </c>
     </row>
     <row r="40">
@@ -1215,11 +1215,11 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ginecológico</t>
+          <t>Respiratorio</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45832.57915509259</v>
+        <v>45881.70859953704</v>
       </c>
     </row>
     <row r="41">
@@ -1235,11 +1235,11 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Respiratorio</t>
+          <t>Neurológico</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46168.92653935185</v>
+        <v>45728.17775462963</v>
       </c>
     </row>
     <row r="42">
@@ -1255,11 +1255,11 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Respiratorio</t>
+          <t>Neurológico</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45687.26846064815</v>
+        <v>46168.99439814815</v>
       </c>
     </row>
     <row r="43">
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45732.42425925926</v>
+        <v>46019.94126157407</v>
       </c>
     </row>
     <row r="44">
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46064.80703703704</v>
+        <v>45932.39643518518</v>
       </c>
     </row>
     <row r="45">
@@ -1315,11 +1315,11 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Respiratorio</t>
+          <t>Digestivo</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46055.29847222222</v>
+        <v>45765.39105324074</v>
       </c>
     </row>
     <row r="46">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45816.11782407408</v>
+        <v>45883.89201388889</v>
       </c>
     </row>
     <row r="47">
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45790.08143518519</v>
+        <v>45953.61700231482</v>
       </c>
     </row>
     <row r="48">
@@ -1375,11 +1375,11 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Neurológico</t>
+          <t>Cardiovascular</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45798.69650462963</v>
+        <v>45918.86324074074</v>
       </c>
     </row>
     <row r="49">
@@ -1395,11 +1395,11 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Traumatológico</t>
+          <t>Digestivo</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45839.48883101852</v>
+        <v>46022.46793981481</v>
       </c>
     </row>
     <row r="50">
@@ -1415,11 +1415,11 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Traumatológico</t>
+          <t>Respiratorio</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45995.27770833333</v>
+        <v>45885.80498842592</v>
       </c>
     </row>
     <row r="51">
@@ -1439,7 +1439,7 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45851.10366898148</v>
+        <v>45821.2409837963</v>
       </c>
     </row>
     <row r="52">
@@ -1455,11 +1455,11 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Neurológico</t>
+          <t>Digestivo</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46011.56509259259</v>
+        <v>46116.62292824074</v>
       </c>
     </row>
     <row r="53">
@@ -1475,11 +1475,11 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Respiratorio</t>
+          <t>Cardiovascular</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46192.96271990741</v>
+        <v>45815.06239583333</v>
       </c>
     </row>
     <row r="54">
@@ -1495,11 +1495,11 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cardiovascular</t>
+          <t>Traumatológico</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46116.02483796296</v>
+        <v>46120.60916666667</v>
       </c>
     </row>
     <row r="55">
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46042.28896990741</v>
+        <v>45777.10414351852</v>
       </c>
     </row>
     <row r="56">
@@ -1535,11 +1535,11 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cardiovascular</t>
+          <t>Neurológico</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46060.05144675926</v>
+        <v>45741.50119212963</v>
       </c>
     </row>
     <row r="57">
@@ -1555,11 +1555,11 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Traumatológico</t>
+          <t>Neurológico</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46153.96219907407</v>
+        <v>46144.53875</v>
       </c>
     </row>
     <row r="58">
@@ -1575,11 +1575,11 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Traumatológico</t>
+          <t>Ginecológico</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45673.66804398148</v>
+        <v>45952.21445601852</v>
       </c>
     </row>
     <row r="59">
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45867.32126157408</v>
+        <v>45895.57568287037</v>
       </c>
     </row>
     <row r="60">
@@ -1615,11 +1615,11 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Respiratorio</t>
+          <t>Digestivo</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45918.92635416667</v>
+        <v>45890.42809027778</v>
       </c>
     </row>
     <row r="61">
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45711.03775462963</v>
+        <v>46170.26004629629</v>
       </c>
     </row>
     <row r="62">
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45731.72741898148</v>
+        <v>46082.93002314815</v>
       </c>
     </row>
     <row r="63">
@@ -1675,11 +1675,11 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Digestivo</t>
+          <t>Traumatológico</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45960.98581018519</v>
+        <v>46163.05605324074</v>
       </c>
     </row>
     <row r="64">
@@ -1695,11 +1695,11 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Digestivo</t>
+          <t>Traumatológico</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45821.9065625</v>
+        <v>46142.74866898148</v>
       </c>
     </row>
     <row r="65">
@@ -1715,11 +1715,11 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Neurológico</t>
+          <t>Ginecológico</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46107.64009259259</v>
+        <v>45830.54916666666</v>
       </c>
     </row>
     <row r="66">
@@ -1735,11 +1735,11 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ginecológico</t>
+          <t>Cardiovascular</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45924.90837962963</v>
+        <v>45836.7409837963</v>
       </c>
     </row>
     <row r="67">
@@ -1755,11 +1755,11 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cardiovascular</t>
+          <t>Ginecológico</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45671.00200231482</v>
+        <v>46109.03868055555</v>
       </c>
     </row>
     <row r="68">
@@ -1775,11 +1775,11 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Neurológico</t>
+          <t>Digestivo</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46046.56403935186</v>
+        <v>45951.69903935185</v>
       </c>
     </row>
     <row r="69">
@@ -1795,11 +1795,11 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ginecológico</t>
+          <t>Cardiovascular</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45902.25296296296</v>
+        <v>45865.43204861111</v>
       </c>
     </row>
     <row r="70">
@@ -1815,11 +1815,11 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ginecológico</t>
+          <t>Respiratorio</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45679.86655092592</v>
+        <v>45906.69171296297</v>
       </c>
     </row>
     <row r="71">
@@ -1835,11 +1835,11 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Traumatológico</t>
+          <t>Ginecológico</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46146.12131944444</v>
+        <v>45846.33339120371</v>
       </c>
     </row>
     <row r="72">
@@ -1855,11 +1855,11 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Respiratorio</t>
+          <t>Traumatológico</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45949.5381712963</v>
+        <v>45745.85908564815</v>
       </c>
     </row>
     <row r="73">
@@ -1875,11 +1875,11 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Traumatológico</t>
+          <t>Neurológico</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46051.92979166667</v>
+        <v>45973.44078703703</v>
       </c>
     </row>
     <row r="74">
@@ -1895,11 +1895,11 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Respiratorio</t>
+          <t>Neurológico</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46057.70438657407</v>
+        <v>45807.26614583333</v>
       </c>
     </row>
     <row r="75">
@@ -1915,11 +1915,11 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Neurológico</t>
+          <t>Respiratorio</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46170.55111111111</v>
+        <v>46184.55297453704</v>
       </c>
     </row>
     <row r="76">
@@ -1935,11 +1935,11 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ginecológico</t>
+          <t>Neurológico</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46114.08017361111</v>
+        <v>45861.55819444444</v>
       </c>
     </row>
     <row r="77">
@@ -1955,11 +1955,11 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Traumatológico</t>
+          <t>Respiratorio</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45663.2419212963</v>
+        <v>45936.99243055555</v>
       </c>
     </row>
     <row r="78">
@@ -1975,11 +1975,11 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Neurológico</t>
+          <t>Traumatológico</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45825.37965277778</v>
+        <v>46099.8322337963</v>
       </c>
     </row>
     <row r="79">
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45922.88674768519</v>
+        <v>45666.26857638889</v>
       </c>
     </row>
     <row r="80">
@@ -2015,11 +2015,11 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Neurológico</t>
+          <t>Digestivo</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45864.02399305555</v>
+        <v>45966.07037037037</v>
       </c>
     </row>
     <row r="81">
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46166.33243055556</v>
+        <v>45679.94488425926</v>
       </c>
     </row>
     <row r="82">
@@ -2055,11 +2055,11 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cardiovascular</t>
+          <t>Traumatológico</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46029.09756944444</v>
+        <v>46002.69232638889</v>
       </c>
     </row>
     <row r="83">
@@ -2075,11 +2075,11 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Respiratorio</t>
+          <t>Digestivo</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45976.99791666667</v>
+        <v>45985.34900462963</v>
       </c>
     </row>
     <row r="84">
@@ -2095,11 +2095,11 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Respiratorio</t>
+          <t>Cardiovascular</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45966.37023148148</v>
+        <v>46097.32226851852</v>
       </c>
     </row>
     <row r="85">
@@ -2119,7 +2119,7 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45757.06414351852</v>
+        <v>46119.15498842593</v>
       </c>
     </row>
     <row r="86">
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46043.88341435185</v>
+        <v>46166.79626157408</v>
       </c>
     </row>
     <row r="87">
@@ -2155,11 +2155,11 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Neurológico</t>
+          <t>Ginecológico</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45958.79721064815</v>
+        <v>45715.55028935185</v>
       </c>
     </row>
     <row r="88">
@@ -2175,11 +2175,11 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Ginecológico</t>
+          <t>Neurológico</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46194.03011574074</v>
+        <v>46130.05189814815</v>
       </c>
     </row>
     <row r="89">
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45716.03141203704</v>
+        <v>46090.0199074074</v>
       </c>
     </row>
     <row r="90">
@@ -2215,11 +2215,11 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ginecológico</t>
+          <t>Respiratorio</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45786.50896990741</v>
+        <v>45919.69423611111</v>
       </c>
     </row>
     <row r="91">
@@ -2235,11 +2235,11 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Ginecológico</t>
+          <t>Neurológico</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46152.69228009259</v>
+        <v>45803.49342592592</v>
       </c>
     </row>
     <row r="92">
@@ -2255,11 +2255,11 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Ginecológico</t>
+          <t>Traumatológico</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45846.25195601852</v>
+        <v>46155.88275462963</v>
       </c>
     </row>
     <row r="93">
@@ -2275,11 +2275,11 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Cardiovascular</t>
+          <t>Ginecológico</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45921.36484953704</v>
+        <v>46170.16988425926</v>
       </c>
     </row>
     <row r="94">
@@ -2295,11 +2295,11 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Traumatológico</t>
+          <t>Respiratorio</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45715.47403935185</v>
+        <v>46164.64763888889</v>
       </c>
     </row>
     <row r="95">
@@ -2319,7 +2319,7 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46159.21734953704</v>
+        <v>45818.4146412037</v>
       </c>
     </row>
     <row r="96">
@@ -2335,11 +2335,11 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cardiovascular</t>
+          <t>Digestivo</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46083.91355324074</v>
+        <v>46108.30792824074</v>
       </c>
     </row>
     <row r="97">
@@ -2355,11 +2355,11 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Cardiovascular</t>
+          <t>Ginecológico</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45863.92325231482</v>
+        <v>45754.9690162037</v>
       </c>
     </row>
     <row r="98">
@@ -2375,11 +2375,11 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Traumatológico</t>
+          <t>Cardiovascular</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45913.06111111111</v>
+        <v>45765.091875</v>
       </c>
     </row>
     <row r="99">
@@ -2395,11 +2395,11 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Neurológico</t>
+          <t>Digestivo</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45659.87841435185</v>
+        <v>45736.60739583334</v>
       </c>
     </row>
     <row r="100">
@@ -2415,11 +2415,11 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Respiratorio</t>
+          <t>Neurológico</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45788.63957175926</v>
+        <v>45823.12872685185</v>
       </c>
     </row>
     <row r="101">
@@ -2435,11 +2435,11 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Digestivo</t>
+          <t>Ginecológico</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45694.04119212963</v>
+        <v>45931.12064814815</v>
       </c>
     </row>
   </sheetData>
